--- a/docs/covariate_datasets_recommendation.xlsx
+++ b/docs/covariate_datasets_recommendation.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,15 @@
       <b val="1"/>
       <color rgb="002F5496"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
     </font>
   </fonts>
   <fills count="6">
@@ -79,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -93,11 +102,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,6 +142,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -486,592 +530,950 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>协变量名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>适用市场</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>影响路径</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>数据源</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>API/URL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>原始频率</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>对齐频率</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>时间覆盖</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>免费?</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>实际状态</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>实测结论(Chronos2)</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>文献支撑</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Henry Hub 天然气现货价</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ERCOT / PJM / CAISO / NYISO</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>燃气机组是边际出清机组，气价直接决定边际发电成本→电价</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>EIA (U.S. Energy Information Administration)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>https://api.eia.gov/ 
-Series: NG.RNGWHHD.D</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>燃气机组是边际出清机组，气价→边际发电成本→电价</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>EIA</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>https://api.eia.gov/ Series: NG.RNGWHHD.D</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>日频</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>日→小时 (forward-fill)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>1997至今</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Apergis &amp; Bowden 2017 (Energy); iScience 2023 新英格兰电气价格耦合; Dallas Fed Energy Indicators</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>最高优先级。四个市场通用，ERCOT燃气占比43-47%，PJM宾州燃气占比60%</t>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>日→小时 (ffill+shift24)</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>❌ 无效：ERCOT ΔMAE +0.58（有害），PJM −0.03（噪声）</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>Apergis &amp; Bowden 2017; iScience 2023</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>日频ffill摊平+滞后1天→起报时旧值，对小时级电价无边际信息</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>天然气库存 (地下储气量)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ERCOT / PJM / CAISO / NYISO</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>库存水平影响气价预期→间接影响电价；冬季库存低时气价/电价飙升</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EIA Weekly Natural Gas Storage Report</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>https://api.eia.gov/ 
-Series: NG.NW2_EPG0_SWO_R48_BCF.W</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>天然气库存(地下储气量)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>库存水平影响气价预期→间接影响电价</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>EIA Weekly Storage Report</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>https://api.eia.gov/ Series: NG.NW2_EPG0_SWO_R48_BCF.W</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>周频</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>周→小时 (forward-fill)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>2010至今</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>EIA Today in Energy 系列文章; NBER Working Paper 21627</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>反映供给侧预期，与气价互补</t>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>周→小时 (ffill+shift168)</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>未单测（与气价共线，代表集略）</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>EIA Today in Energy; NBER WP 21627</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>周频ffill整周一个值，时效性更差</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>HRC 热轧卷板钢价 (期货/指数)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>HRC 钢价（热轧卷板期货）</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>PJM</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>钢厂(电弧炉)是PJM覆盖区(Ohio 12%, PA 4%)的高耗电工业→钢价高→开工多→负荷增→电价上行</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FRED (PPI: Iron and Steel)
-CME HRC Futures</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/ 
-Series: PCU33113311
-CME: HRC1!</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>月频(PPI) / 日频(期货)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>月→小时 (forward-fill) 或 日→小时</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>PPI: 1985至今
-期货: 2008至今</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>PPI免费
-期货需数据商</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>USGS MCS 2026: Ohio 8% + PA 4% 粗钢产量; EIA Manufacturing Energy Consumption Survey (MECS)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>老师会议点名。注意：最大产钢州Indiana在MISO不在PJM，需论文中谨慎措辞</t>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>钢厂(电弧炉)是PJM高耗电工业→钢价高→开工→负荷→电价</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FRED/CME HRC Futures</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CME: HRC1!  日频HRC期货（已替换原月度PPI）</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>日频</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>日→小时 (ffill+shift24)</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成（改用日频HRC，弃用月度PPI）</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>❌ 无效：PJM ΔMAE +0.45（有害），Spike-F1 −0.0105</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>USGS MCS 2026; EIA MECS</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>老师会议点名。日频ffill+滞后后仍失效，'钢厂→电价'假设被证伪</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>美国粗钢周产量 / 产能利用率</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>粗钢周产量/产能利用率(AISI)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>PJM</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>产量直接反映电弧炉开工→工业负荷→电价</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>AISI (American Iron and Steel Institute) 周报
-FRED 工业生产指数</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/ 
-Series: IPG3311A2S (钢铁工业生产指数)
-AISI: steel.org/industry-data/</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>周频(AISI) / 月频(FRED)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>周/月→小时 (forward-fill)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>1972至今</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>FRED免费
-AISI需注册</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>USGS MCS 2024/2025/2026; EIA steel industry energy brief</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>与钢价搭配使用，构成完整的'钢厂→电价'故事</t>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>产量反映电弧炉开工→工业负荷→电价</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>AISI周报 / FRED工业生产指数</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>FRED: IPG3311A2S  AISI: steel.org</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>周/月频</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>❌ 未做</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>未下载。改用日频HRC钢价替代，故未实现</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>USGS MCS; EIA steel brief</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>原计划项，实施时被日频HRC期货取代</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>原油价格 (WTI)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>WTI 原油价</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ERCOT</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>德州经济以油气为核心，油价影响产业开工→工业用电需求；油价也间接影响气价</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>油价影响产业开工→工业用电需求；间接影响气价</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>EIA / FRED</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>https://api.eia.gov/ 
-Series: PET.RCLC1.D
-FRED: DCOILWTICO</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>FRED: DCOILWTICO</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>日频</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>日→小时 (forward-fill)</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>1986至今</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>EIA Energy &amp; Financial Markets; 达拉斯联储能源指标</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>对ERCOT有独特意义，其他市场优先级低</t>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>日→小时 (ffill+shift24)</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>❌ 有害：ERCOT ΔMAE +0.52（变差）</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>EIA Energy &amp; Financial Markets; Dallas Fed</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>日频ffill+滞后失效，对ERCOT无边际信息</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>LLM 新闻情绪特征</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ERCOT / PJM / CAISO / NYISO</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>极端事件(寒潮/热浪/设备故障/政策变化)通过新闻传导→影响市场预期→影响电价spike</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>见Sheet 3「新闻特征方案」</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GDELT / Google News API / newsapi.org / 财经RSS</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>不定</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>日→小时 (同日填充)</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>取决于数据源</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>GDELT免费
-newsapi有限免费</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>会议纪要第六节: '用LLM将新闻变成参数'</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>工作量最大，建议最后做。详见Sheet 3</t>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>LLM新闻情绪特征(GDELT)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>极端事件经新闻传导→市场预期→电价spike</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>GDELT（路径A：情绪打分）</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>gdeltproject.org</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>15分钟→日</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>日→小时 (次日ffill)</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已下载处理（路径A）</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>未测：未纳入model_ready，本次扫描未覆盖</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>会议纪要第六节'用LLM将新闻变成参数'</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>已生成4市场news_hourly.csv，但未接入模型。详见Sheet3更新</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>碳排放配额价格 (RGGI)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>NYISO / PJM (部分州)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>RGGI碳价是东北部电厂的额外成本→推高边际发电成本</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>RGGI Inc. 官网拍卖结果</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>碳排放配额(RGGI)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>NYISO/PJM(部分)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>RGGI碳价是东北部电厂额外成本→边际发电成本</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>RGGI Inc.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>https://www.rggi.org/auctions/auction-results</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>季度拍卖 + 二级市场日频</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>季度/日→小时 (forward-fill)</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2009至今</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>RGGI官方报告; Fell &amp; Maniloff (2018, JEEM)</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>仅对RGGI覆盖州有效(NY, PA部分)。影响较小，可选做</t>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>季度拍卖</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>❌ 未做</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>未下载</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Fell &amp; Maniloff 2018 JEEM</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>仅RGGI覆盖州，影响小，可选做</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>区域间输电潮流 (interchange)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ERCOT / PJM / CAISO / NYISO</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>跨区输电影响本地供需平衡→影响电价</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>EIA (已有)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>区域间输电潮流(interchange)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>跨区输电影响本地供需→电价</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>EIA(已有)</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>data/raw/EIA/csv/interchange/</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>小时频</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>已对齐</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>已有</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>你已有这些数据但可能未使用</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>不需要额外下载，检查是否已纳入模型</t>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>❌ 未做</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>未纳入model_ready</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>数据已有但未接入模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>负荷预报(load)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>需求侧主驱动，直接决定电价</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>EIA Grid Monitor 日前负荷预报</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>15_build_forecast_model_ready.py</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>小时频(预报)</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>预报版直接对齐(不ffill)</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>✅ PJM赢家：ΔMAE −0.89(−3.4%)，Spike-F1 +0.022；ERCOT有害(+0.42但Spike-F1升)</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>原生小时频+日前预报，不经ffill，是PJM唯一有效协变量</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>温度预报(temperature)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>取暖制冷需求→负荷→电价</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Open-Meteo Historical Forecast</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>11_download_temp_forecast.py</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>小时频(预报)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>预报版直接对齐(不ffill)</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>❌ 有害：ERCOT +0.26、PJM +0.25（均变差）</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>预报质量没问题，但Chronos2零样本不会转化为价格信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>风电预报(wind)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/CAISO</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>风电出力直接决定ERCOT电价</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Open-Meteo wind_speed_10m(风速代理)</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>14_download_wind_solar_forecast_proxy.py</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>小时频(预报)</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>预报版直接对齐(不ffill)</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>✅ ERCOT赢家：ΔMAE −0.60(−3.6%)，rMAE 0.770→0.738</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>风速代理非真实发电量，但相关性够强。ERCOT风电渗透率高故有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>光伏预报(solar)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/CAISO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>光伏出力影响日间电价</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Open-Meteo shortwave_radiation(辐射代理)</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>14_download_wind_solar_forecast_proxy.py</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>小时频(预报)</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>预报版直接对齐(不ffill)</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>微弱：ERCOT ΔMAE −0.15(−0.9%)</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>辐射代理较弱，效果不及wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>风暴事件(NOAA)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>风暴冲击供需→尖峰</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>NOAA Storm Events</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>05_download_noaa_storm.py</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>日频</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>日→小时 (ffill+shift24)</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>❌ 有害：ERCOT +0.29、PJM +0.93(全场最差)</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>事后统计+滞后1天，对日前预测是噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>发电结构(gas_share等8列)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>ERCOT/PJM/CAISO/NYISO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>天然气占比=边际定价；可再生骤变→尖峰</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>EIA Fuel Mix</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>06_eia_fuel_mix_features.py</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>小时频</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>小时→小时 (shift24)</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>基本无效：gas_share两边变差；renewable_shock ERCOT微弱(Spike-F1+0.012)</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>小时频无ffill，但shift24滞后+模型不会用→失效。8列共线，仅测2代表</t>
         </is>
       </c>
     </row>
@@ -1087,301 +1489,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>任务</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>预计工时</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>验证方法</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>实际状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>第1步
-(本周)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>下载 Henry Hub 天然气日频价格
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>第1步</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>下载Henry Hub天然气日频价格
 对齐到电价时间轴
-算与4市场电价的相关性</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2-3小时</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+算与4市场电价相关性</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2-3h</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>EIA API Key
-你的电价CSV</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>data/raw/covariates/henry_hub_daily.csv
-相关性分析图表</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Pearson/Spearman相关系数
-滞后交叉相关分析
-可视化scatter plot</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+电价CSV</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>data/covariates/gas/cleaned/henry_hub_daily.csv</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Pearson/Spearman相关
+滞后交叉相关
+scatter plot</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成。但Chronos2实测有害(ERCOT ΔMAE +0.58)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>第1步
-(本周)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>第1步</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>下载天然气库存周报
 对齐时间轴</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>1小时</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>EIA API Key</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>data/raw/covariates/natgas_storage_weekly.csv</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>数据完整性检查
-时间范围覆盖验证</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>data/covariates/gas/cleaned/natgas_storage_weekly.csv</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性
+时间覆盖验证</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成。未单测(与气价共线)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>第2步
-(下周)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>下载FRED钢铁PPI月度指数
-下载AISI粗钢周产量
-对齐时间轴</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2-3小时</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>FRED API Key
-AISI数据</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>data/raw/covariates/steel_ppi_monthly.csv
-data/raw/covariates/crude_steel_weekly.csv</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>与PJM电价做相关分析
-可视化时序叠加图</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>第2步</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>下载钢价(改用日频HRC期货，弃用月度PPI)
+下载AISI粗钢周产量</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2-3h</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FRED/CME
+AISI</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>data/covariates/steel/cleaned/hrc_futures_daily.csv</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>与PJM电价相关分析
+时序叠加图</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>部分完成：日频HRC已做(实测有害PJM +0.45)；AISI粗钢周产量未做(被HRC替代)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>第2步
-(下周)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>第2步</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>下载WTI原油日频价格
 对齐时间轴</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1小时</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>EIA/FRED API</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>data/raw/covariates/wti_crude_daily.csv</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>data/covariates/oil/cleaned/wti_crude_daily.csv</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>与ERCOT电价相关分析</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成。Chronos2实测有害(ERCOT ΔMAE +0.52)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>第3步
-(第3周)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>将所有P0/P1协变量
-集成到模型训练pipeline
-跑一轮参数消融</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>第3步</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>P0/P1协变量集成到pipeline
+跑参数消融</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>1-2天</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>上述所有协变量CSV
-现有消融框架</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>新的消融实验结果
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>协变量CSV
+消融框架</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>ablation_A结果
 MAE/Spike-F1对比表</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>A/B对比: 有vs无协变量
-显著性检验</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>A/B对比:有vs无
+显著性检验(DM test)</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成。ablation_A_covariates_no_lear.yaml(11模型)。发现仅Chronos2消费协变量，其余10模型降级</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>第4步
-(后续)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>新闻特征工程（详见Sheet 3）</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>第3步+</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Chronos2单协变量扫描(本次新增)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>0.5天</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>预报版model_ready</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>scan_ercot/pjm_forecast.csv</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>逐协变量ΔMAE/ΔSpike-F1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>✅ 已完成。结论:仅wind(ERCOT)/load(PJM)有效；经济风暴类ffill+滞后失效；MAE与Spike-F1解耦</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>第4步</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>新闻特征工程(GDELT路径A)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>1-2周</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>新闻数据源
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>GDELT
 LLM API</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>data/raw/covariates/news_sentiment_daily.csv</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>data/covariates/news/hourly/*_news_hourly.csv</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>消融验证
-特征重要性排序</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>待开始</t>
+特征重要性</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>部分完成：GDELT情绪已下载处理4市场，但未纳入model_ready、未测。详见Sheet3</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1783,6 +2212,130 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>═══ 实际执行情况更新（2026-07-15）═══</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>采用路径</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>路径A（GDELT + 情绪打分）已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>scripts/covariates/08_download_gdelt_news.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>data/covariates/news/hourly/{ercot,pjm,caiso,nyiso}_news_hourly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>对齐方式</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>次日forward-fill：day T 新闻特征从 day T+1 00:00 UTC 生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>接入状态</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>❌ 未纳入 model_ready，本次 Chronos2 扫描未覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr"/>
+      <c r="B49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>新闻特征有效性尚未验证。鉴于 P0/P1 经济类协变量实测集体失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr"/>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>（ffill+滞后导致时效性丧失），新闻情绪同为日频次日ffill，</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr"/>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>存在相同失效风险，接入前需先单独扫描验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr"/>
+      <c r="B53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>后续</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>如要验证，可用 run_chronos2_covariate_scan.py --covariates news_tone 之类扩展</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A16:F16"/>
@@ -1790,8 +2343,8 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
